--- a/data/lönegap_kön.xlsx
+++ b/data/lönegap_kön.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://svenskidrott-my.sharepoint.com/personal/william_lind_rfsisu_se/Documents/Dokument/GitHub/Hemsideprojekt/Hemsideprojekt/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://svenskidrott-my.sharepoint.com/personal/william_lind_rfsisu_se/Documents/Dokument/GitHub/RF-SISU Uppland/sverige-i-siffror/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59" documentId="11_F25DC773A252ABDACC1048F9A9DA43CE5ADE58FD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7DC7923F-87E3-494C-A5D2-3E3A2B01454D}"/>
+  <xr:revisionPtr revIDLastSave="65" documentId="11_F25DC773A252ABDACC1048F9A9DA43CE5ADE58FD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84F3A1DD-88E4-4B58-83A8-34F0B22B9136}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1680" yWindow="3345" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="17">
   <si>
     <t>Land</t>
   </si>
@@ -70,6 +70,12 @@
   </si>
   <si>
     <t>7.0</t>
+  </si>
+  <si>
+    <t>7.5</t>
+  </si>
+  <si>
+    <t>7.8</t>
   </si>
 </sst>
 </file>
@@ -130,8 +136,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3AC87FE9-4383-4503-A34C-AC04D58489E9}" name="Tabell1" displayName="Tabell1" ref="A1:D11" totalsRowShown="0">
-  <autoFilter ref="A1:D11" xr:uid="{3AC87FE9-4383-4503-A34C-AC04D58489E9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3AC87FE9-4383-4503-A34C-AC04D58489E9}" name="Tabell1" displayName="Tabell1" ref="A1:D13" totalsRowShown="0">
+  <autoFilter ref="A1:D13" xr:uid="{3AC87FE9-4383-4503-A34C-AC04D58489E9}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{EDE7E4B8-D2DF-4FCF-9D8B-0BAE13EFA48E}" name="Land"/>
     <tableColumn id="2" xr3:uid="{AB65221E-C6C1-4DB4-80A5-3324D991AD7A}" name="Kod"/>
@@ -405,13 +411,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="8.7265625" style="1"/>
+    <col min="4" max="4" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -425,7 +431,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -439,7 +445,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -453,7 +459,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -467,7 +473,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -481,7 +487,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -495,7 +501,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -509,7 +515,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -523,7 +529,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -537,7 +543,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -551,7 +557,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -563,6 +569,34 @@
       </c>
       <c r="D11" s="1" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12">
+        <v>2024</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13">
+        <v>2025</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -575,6 +609,6 @@
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{eb5b2d6e-028e-454d-b878-0c055adbeb2a}" enabled="0" method="" siteId="{eb5b2d6e-028e-454d-b878-0c055adbeb2a}" removed="1"/>
+  <clbl:label id="{e782e157-8ece-4105-b8e9-fe1eecbfcd69}" enabled="1" method="Privileged" siteId="{eb5b2d6e-028e-454d-b878-0c055adbeb2a}" removed="0"/>
 </clbl:labelList>
 </file>